--- a/314e-ig/output/StructureDefinition-observation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -324,7 +324,7 @@
     <t>Observation.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta
+    <t xml:space="preserve">Meta {http://314e.com/fhir/StructureDefinition/meta-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-observation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-observation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-observation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$64</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2489" uniqueCount="487">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -644,10 +644,12 @@
 </t>
   </si>
   <si>
-    <t>(QI) Classification of type of observation</t>
-  </si>
-  <si>
-    <t>A code that classifies the general type of observation being made.</t>
+    <t>Operational procedure/service categories</t>
+  </si>
+  <si>
+    <t>Broad and optional subcategory classifications used
+for workflow, routing, analytics, and operational
+grouping of Observation resources.</t>
   </si>
   <si>
     <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
@@ -681,10 +683,45 @@
     <t>Classification of  type of observation</t>
   </si>
   <si>
+    <t>A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
     <t>Note that other codes are permitted, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/STU7/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-simple-observation-category</t>
+  </si>
+  <si>
+    <t>Observation.category:broadCategory</t>
+  </si>
+  <si>
+    <t>broadCategory</t>
+  </si>
+  <si>
+    <t>Required broad procedure/service category</t>
+  </si>
+  <si>
+    <t>Top-level operational classification of the
+observation.</t>
+  </si>
+  <si>
+    <t>http://314e.com/fhir/ValueSet/procedure-category-broad-314e</t>
+  </si>
+  <si>
+    <t>Observation.category:subCategory</t>
+  </si>
+  <si>
+    <t>subCategory</t>
+  </si>
+  <si>
+    <t>Optional detailed subcategory</t>
+  </si>
+  <si>
+    <t>More granular operational sub-classification of the
+observation.</t>
+  </si>
+  <si>
+    <t>http://314e.com/fhir/ValueSet/procedure-category-subcategory-314e</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1827,12 +1864,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP62"/>
+  <dimension ref="A1:AP64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.84765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="48.84765625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.8671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -3835,7 +3872,7 @@
         <v>210</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>201</v>
@@ -3869,10 +3906,10 @@
         <v>189</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3925,14 +3962,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>214</v>
+        <v>20</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3948,22 +3987,22 @@
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>198</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3988,13 +4027,11 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -4012,13 +4049,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -4027,38 +4064,40 @@
         <v>104</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>221</v>
+        <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>223</v>
+        <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>226</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>92</v>
@@ -4070,22 +4109,22 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4110,13 +4149,11 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -4134,13 +4171,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -4149,44 +4186,44 @@
         <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>233</v>
+        <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>20</v>
+        <v>225</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
@@ -4195,18 +4232,20 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
       </c>
@@ -4230,13 +4269,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>20</v>
+        <v>230</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -4254,13 +4293,13 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
@@ -4269,44 +4308,44 @@
         <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>236</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>244</v>
+        <v>20</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
@@ -4315,19 +4354,19 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4376,7 +4415,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4391,44 +4430,44 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
@@ -4437,20 +4476,18 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
       </c>
@@ -4498,13 +4535,13 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
@@ -4513,19 +4550,19 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>20</v>
@@ -4533,14 +4570,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4559,18 +4596,20 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
@@ -4618,7 +4657,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4633,19 +4672,19 @@
         <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>20</v>
@@ -4653,21 +4692,21 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>93</v>
@@ -4679,17 +4718,19 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O24" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4738,13 +4779,13 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
@@ -4753,19 +4794,19 @@
         <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>20</v>
@@ -4773,10 +4814,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4790,7 +4831,7 @@
         <v>92</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
@@ -4799,20 +4840,18 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4848,17 +4887,19 @@
         <v>20</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AC25" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4867,7 +4908,7 @@
         <v>92</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>289</v>
+        <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>104</v>
@@ -4876,27 +4917,27 @@
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>290</v>
+        <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>20</v>
+        <v>283</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>293</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4907,31 +4948,29 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>198</v>
+        <v>285</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4956,13 +4995,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>299</v>
+        <v>20</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>301</v>
+        <v>20</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4980,34 +5019,34 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>302</v>
+        <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>135</v>
+        <v>290</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>20</v>
+        <v>292</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>20</v>
@@ -5015,45 +5054,45 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>305</v>
+        <v>20</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>198</v>
+        <v>294</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5078,40 +5117,38 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB27" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="Y27" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>20</v>
-      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>104</v>
@@ -5120,27 +5157,27 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>315</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5151,7 +5188,7 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -5163,19 +5200,19 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>317</v>
+        <v>198</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5200,13 +5237,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>20</v>
+        <v>310</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>20</v>
+        <v>311</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>20</v>
+        <v>312</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5224,16 +5261,16 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>20</v>
+        <v>313</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>104</v>
@@ -5245,10 +5282,10 @@
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>322</v>
+        <v>135</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -5259,21 +5296,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5288,15 +5325,17 @@
         <v>198</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -5320,13 +5359,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5344,13 +5383,13 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
@@ -5362,27 +5401,27 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5393,7 +5432,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5405,19 +5444,19 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>198</v>
+        <v>328</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5442,13 +5481,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>328</v>
+        <v>20</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>340</v>
+        <v>20</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>341</v>
+        <v>20</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5466,13 +5505,13 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
@@ -5487,10 +5526,10 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -5501,10 +5540,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5527,16 +5566,16 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>345</v>
+        <v>198</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5562,13 +5601,13 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>20</v>
+        <v>339</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>20</v>
+        <v>340</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>20</v>
+        <v>341</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5586,7 +5625,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5604,27 +5643,27 @@
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>352</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5647,18 +5686,20 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>354</v>
+        <v>198</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5682,13 +5723,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>20</v>
+        <v>339</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>20</v>
+        <v>351</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>20</v>
+        <v>352</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5706,7 +5747,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5724,27 +5765,27 @@
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>358</v>
+        <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5755,7 +5796,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5767,20 +5808,18 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5828,45 +5867,45 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AG33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>370</v>
-      </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>20</v>
+        <v>363</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5889,15 +5928,17 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5946,7 +5987,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5958,37 +5999,37 @@
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>20</v>
+        <v>369</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>20</v>
+        <v>370</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>20</v>
+        <v>372</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6007,18 +6048,20 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>137</v>
+        <v>374</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
@@ -6066,7 +6109,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6078,7 +6121,7 @@
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>143</v>
+        <v>379</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -6087,10 +6130,10 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -6101,46 +6144,42 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>382</v>
+        <v>20</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>137</v>
+        <v>383</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
       </c>
@@ -6188,19 +6227,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -6212,7 +6251,7 @@
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>135</v>
+        <v>387</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6223,21 +6262,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6249,15 +6288,17 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>387</v>
+        <v>137</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6306,19 +6347,19 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -6327,10 +6368,10 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -6341,33 +6382,33 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>387</v>
+        <v>137</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>394</v>
@@ -6375,8 +6416,12 @@
       <c r="M38" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="N38" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6424,19 +6469,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -6445,10 +6490,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>396</v>
+        <v>135</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6485,20 +6530,16 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>198</v>
+        <v>398</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N39" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="O39" t="s" s="2">
-        <v>401</v>
-      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6522,13 +6563,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>402</v>
+        <v>20</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>403</v>
+        <v>20</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6555,7 +6596,7 @@
         <v>92</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>20</v>
+        <v>401</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>104</v>
@@ -6564,13 +6605,13 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>404</v>
+        <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>314</v>
+        <v>403</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -6581,10 +6622,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6595,7 +6636,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6607,20 +6648,16 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>198</v>
+        <v>398</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6644,13 +6681,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>328</v>
+        <v>20</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>411</v>
+        <v>20</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>412</v>
+        <v>20</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6668,16 +6705,16 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>20</v>
+        <v>401</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>104</v>
@@ -6686,13 +6723,13 @@
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>404</v>
+        <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>314</v>
+        <v>407</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -6703,10 +6740,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6729,17 +6766,19 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>414</v>
+        <v>198</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="O41" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6764,13 +6803,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>20</v>
+        <v>413</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>20</v>
+        <v>414</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6788,7 +6827,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6806,13 +6845,13 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>20</v>
+        <v>415</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>20</v>
+        <v>416</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>418</v>
+        <v>325</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -6823,10 +6862,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6837,7 +6876,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6849,16 +6888,20 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>372</v>
+        <v>198</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6882,13 +6925,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>20</v>
+        <v>339</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>20</v>
+        <v>422</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>20</v>
+        <v>423</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6906,13 +6949,13 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
@@ -6924,13 +6967,13 @@
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>20</v>
+        <v>415</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>422</v>
+        <v>325</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -6941,10 +6984,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6955,7 +6998,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6964,21 +7007,21 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N43" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="O43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
       </c>
@@ -7026,13 +7069,13 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
@@ -7047,7 +7090,7 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>428</v>
+        <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>429</v>
@@ -7075,7 +7118,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -7084,20 +7127,18 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>434</v>
-      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7152,7 +7193,7 @@
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
@@ -7167,10 +7208,10 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>428</v>
+        <v>402</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -7181,10 +7222,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7207,20 +7248,18 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>363</v>
+        <v>435</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="N45" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>440</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
@@ -7268,7 +7307,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7289,10 +7328,10 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7303,10 +7342,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7317,7 +7356,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7326,18 +7365,20 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>372</v>
+        <v>442</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>373</v>
+        <v>443</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7386,19 +7427,19 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>375</v>
+        <v>441</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7407,10 +7448,10 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>20</v>
+        <v>439</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>376</v>
+        <v>446</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7421,14 +7462,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7444,21 +7485,23 @@
         <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>137</v>
+        <v>374</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>378</v>
+        <v>448</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>379</v>
+        <v>449</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7506,7 +7549,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>380</v>
+        <v>447</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7518,7 +7561,7 @@
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -7527,10 +7570,10 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>20</v>
+        <v>452</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>376</v>
+        <v>453</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7541,46 +7584,42 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>382</v>
+        <v>20</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>137</v>
+        <v>383</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7628,19 +7667,19 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
@@ -7652,7 +7691,7 @@
         <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>135</v>
+        <v>387</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -7663,21 +7702,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7686,23 +7725,21 @@
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>198</v>
+        <v>137</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>448</v>
+        <v>390</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
       </c>
@@ -7726,13 +7763,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>328</v>
+        <v>20</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>450</v>
+        <v>20</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7750,34 +7787,34 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>446</v>
+        <v>391</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>451</v>
+        <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>223</v>
+        <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>224</v>
+        <v>387</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>225</v>
+        <v>20</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>20</v>
@@ -7785,45 +7822,45 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>283</v>
+        <v>137</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>453</v>
+        <v>394</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>285</v>
+        <v>395</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>454</v>
+        <v>154</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>287</v>
+        <v>155</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7872,45 +7909,45 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>452</v>
+        <v>396</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>455</v>
+        <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>292</v>
+        <v>135</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>293</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7918,7 +7955,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>92</v>
@@ -7930,22 +7967,22 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>198</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>298</v>
+        <v>229</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7970,13 +8007,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>299</v>
+        <v>339</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>300</v>
+        <v>461</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>301</v>
+        <v>231</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7994,16 +8031,16 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>302</v>
+        <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>104</v>
@@ -8012,16 +8049,16 @@
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>20</v>
+        <v>462</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>135</v>
+        <v>234</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>303</v>
+        <v>235</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>20</v>
@@ -8029,21 +8066,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>305</v>
+        <v>20</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -8052,22 +8089,22 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>198</v>
+        <v>294</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>308</v>
+        <v>465</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8092,13 +8129,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>299</v>
+        <v>20</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>310</v>
+        <v>20</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -8116,13 +8153,13 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
@@ -8134,27 +8171,27 @@
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>312</v>
+        <v>466</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>315</v>
+        <v>304</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8165,7 +8202,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -8177,19 +8214,19 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>363</v>
+        <v>198</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>366</v>
+        <v>470</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>367</v>
+        <v>309</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8214,13 +8251,13 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>20</v>
+        <v>310</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>20</v>
+        <v>311</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>20</v>
+        <v>312</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -8238,16 +8275,16 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>20</v>
+        <v>313</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>104</v>
@@ -8259,10 +8296,10 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>369</v>
+        <v>135</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>370</v>
+        <v>314</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8273,21 +8310,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8299,16 +8336,20 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>372</v>
+        <v>198</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>373</v>
+        <v>472</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
       </c>
@@ -8332,13 +8373,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>20</v>
+        <v>310</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>20</v>
+        <v>321</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>20</v>
+        <v>322</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -8356,49 +8397,49 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>375</v>
+        <v>471</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>20</v>
+        <v>323</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>20</v>
+        <v>324</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>20</v>
+        <v>326</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8417,18 +8458,20 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>137</v>
+        <v>374</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>20</v>
       </c>
@@ -8476,7 +8519,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>380</v>
+        <v>473</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8488,7 +8531,7 @@
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8497,10 +8540,10 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -8511,46 +8554,42 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>382</v>
+        <v>20</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>137</v>
+        <v>383</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>20</v>
       </c>
@@ -8598,19 +8637,19 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8622,7 +8661,7 @@
         <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>135</v>
+        <v>387</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -8633,21 +8672,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8659,15 +8698,17 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>387</v>
+        <v>137</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8716,19 +8757,19 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
@@ -8737,10 +8778,10 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>20</v>
@@ -8751,33 +8792,33 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>387</v>
+        <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>394</v>
@@ -8785,8 +8826,12 @@
       <c r="M58" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+      <c r="N58" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
       </c>
@@ -8834,19 +8879,19 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
@@ -8855,10 +8900,10 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>396</v>
+        <v>135</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
@@ -8869,10 +8914,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8895,20 +8940,16 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>198</v>
+        <v>398</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N59" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="O59" t="s" s="2">
-        <v>401</v>
-      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>20</v>
       </c>
@@ -8932,13 +8973,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>402</v>
+        <v>20</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>471</v>
+        <v>20</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -8965,7 +9006,7 @@
         <v>92</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>20</v>
+        <v>401</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>104</v>
@@ -8974,13 +9015,13 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>404</v>
+        <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>314</v>
+        <v>403</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -8991,10 +9032,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9005,7 +9046,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -9017,20 +9058,16 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>198</v>
+        <v>398</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>20</v>
       </c>
@@ -9054,13 +9091,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>328</v>
+        <v>20</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>411</v>
+        <v>20</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>473</v>
+        <v>20</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9078,16 +9115,16 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>20</v>
+        <v>401</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>104</v>
@@ -9096,13 +9133,13 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>404</v>
+        <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>314</v>
+        <v>407</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
@@ -9113,10 +9150,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9139,17 +9176,19 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>414</v>
+        <v>198</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="O61" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9174,13 +9213,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>20</v>
+        <v>413</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>20</v>
+        <v>482</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -9198,7 +9237,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9216,13 +9255,13 @@
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>20</v>
+        <v>415</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>20</v>
+        <v>416</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>418</v>
+        <v>325</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
@@ -9233,10 +9272,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9247,7 +9286,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -9259,16 +9298,20 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>372</v>
+        <v>198</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>20</v>
       </c>
@@ -9292,13 +9335,13 @@
         <v>20</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>20</v>
+        <v>339</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>20</v>
+        <v>422</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>20</v>
+        <v>484</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
@@ -9316,13 +9359,13 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
@@ -9334,23 +9377,261 @@
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>20</v>
+        <v>415</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>422</v>
+        <v>325</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP62" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP64" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP62">
+  <autoFilter ref="A1:AP64">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9360,7 +9641,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI61">
+  <conditionalFormatting sqref="A2:AI63">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/314e-ig/output/StructureDefinition-observation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -547,7 +547,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/devicerequest-314e|http://314e.com/fhir/StructureDefinition/immunizationrecommendation-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e|http://314e.com/fhir/StructureDefinition/nutritionorder-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -576,7 +576,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/medicationadministration-314e|http://314e.com/fhir/StructureDefinition/medicationdispense-314e|MedicationStatement|http://314e.com/fhir/StructureDefinition/procedure-314e|http://314e.com/fhir/StructureDefinition/immunization-314e|http://314e.com/fhir/StructureDefinition/imagingstudy-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -770,7 +770,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -801,7 +801,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(Resource|http://314e.com/fhir/StructureDefinition/account-314e|http://314e.com/fhir/StructureDefinition/allergyintolerance-314e|http://314e.com/fhir/StructureDefinition/appointment-314e|http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/clinicalimpression-314e|http://314e.com/fhir/StructureDefinition/communicationrequest-314e|http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/contract-314e|http://314e.com/fhir/StructureDefinition/coverage-314e|http://314e.com/fhir/StructureDefinition/detectedissue-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/devicerequest-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e|http://314e.com/fhir/StructureDefinition/encounter-314e|http://314e.com/fhir/StructureDefinition/endpoint-314e|http://314e.com/fhir/StructureDefinition/episodeofcare-314e|http://314e.com/fhir/StructureDefinition/goal-314e|http://314e.com/fhir/StructureDefinition/group-314e|http://314e.com/fhir/StructureDefinition/healthcareservice-314e|http://314e.com/fhir/StructureDefinition/imagingstudy-314e|http://314e.com/fhir/StructureDefinition/immunization-314e|http://314e.com/fhir/StructureDefinition/immunizationevaluation-314e|http://314e.com/fhir/StructureDefinition/immunizationrecommendation-314e|http://314e.com/fhir/StructureDefinition/location-314e|http://314e.com/fhir/StructureDefinition/media-314e|http://314e.com/fhir/StructureDefinition/medication-314e|http://314e.com/fhir/StructureDefinition/medicationadministration-314e|http://314e.com/fhir/StructureDefinition/medicationdispense-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e|http://314e.com/fhir/StructureDefinition/molecularsequence-314e|http://314e.com/fhir/StructureDefinition/nutritionorder-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/procedure-314e|http://314e.com/fhir/StructureDefinition/questionnaireresponse-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/requestgroup-314e|http://314e.com/fhir/StructureDefinition/schedule-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e|http://314e.com/fhir/StructureDefinition/slot-314e|http://314e.com/fhir/StructureDefinition/specimen-314e|http://314e.com/fhir/StructureDefinition/substance-314e|http://314e.com/fhir/StructureDefinition/task-314e|http://314e.com/fhir/StructureDefinition/visionprescription-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -824,7 +824,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -915,7 +915,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-practitioner|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-organization|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-practitionerrole|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-careteam|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-relatedperson) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1137,7 +1137,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/specimen-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1165,7 +1165,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/device-314e|DeviceMetric) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1390,7 +1390,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/questionnaireresponse-314e|http://314e.com/fhir/StructureDefinition/molecularsequence-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1412,7 +1412,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-simple-observation|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-questionnaireresponse|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-imagingstudy|http://hl7.org/fhir/us/core/StructureDefinition/us-core-documentreference|Media|MolecularSequence) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/imagingstudy-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e|http://314e.com/fhir/StructureDefinition/media-314e|http://314e.com/fhir/StructureDefinition/molecularsequence-314e|MolecularSequence) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-observation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-observation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
